--- a/output/2026-09-15_22_Croazia_Brodsko-posavska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-15_22_Croazia_Brodsko-posavska_Impiantistica_aspirazione_industriale.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore/rappresentante ufficiale di macchine e impianti industriali per vuoto e aspirazione: pompe per vuoto e soffianti Elmo Rietschle e Wittig, compressori CompAir, generatori azoto/ossigeno Inmatec, macchine Lissmac; vendita, noleggio e assistenza tecnica. Dato confermato su piu fonti indipendenti (verifica tramite WebSearch, WebFetch bloccato da proxy/DNS).</t>
+          <t>Distributore/rappresentante ufficiale di macchine e impianti industriali per vuoto e aspirazione: pompe per vuoto e soffianti Elmo Rietschle e Wittig, compressori CompAir, generatori azoto/ossigeno Inmatec, macchine Lissmac; vendita, noleggio e assistenza tecnica. Dato confermato su piu fonti indipendenti (verifica tramite WebSearch, WebFetch bloccato da proxy/DNS). [DUPLICATO — vedi anche: 2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
